--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
   <si>
     <t>Mat</t>
   </si>
@@ -97,51 +97,54 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>VEGA</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -169,30 +172,36 @@
     <t>DELGADO</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -217,49 +226,55 @@
     <t>DAMON</t>
   </si>
   <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FLORENTINA ESMERALDA</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>LESLY VIANEY</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>BETZABE</t>
+  </si>
+  <si>
     <t>TOBIAS</t>
   </si>
   <si>
+    <t>LEONOR</t>
+  </si>
+  <si>
     <t>ESTEFANY CELESTE</t>
   </si>
   <si>
     <t>XIMENA</t>
   </si>
   <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
     <t>NERY JOSELYN</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>BETZABE</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
   </si>
   <si>
     <t>EDUARDO EMER</t>
@@ -1196,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,10 +1249,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1257,10 +1272,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1280,10 +1295,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1303,10 +1318,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1326,10 +1341,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1343,16 +1358,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920124</v>
+        <v>22330051920346</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1366,16 +1381,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920126</v>
+        <v>22330051920247</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1389,16 +1404,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920132</v>
+        <v>22330051920348</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1412,16 +1427,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920346</v>
+        <v>22330051920136</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1435,16 +1450,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920247</v>
+        <v>22330051920141</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1458,16 +1473,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920348</v>
+        <v>22330051920354</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1481,22 +1496,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920354</v>
+        <v>22330051920155</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1504,22 +1519,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920258</v>
+        <v>22330051920386</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1527,68 +1542,68 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920155</v>
+        <v>22330051920021</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920386</v>
+        <v>22330051920334</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920021</v>
+        <v>22330051920079</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1596,22 +1611,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920334</v>
+        <v>22330051920112</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1619,22 +1634,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920079</v>
+        <v>22330051920124</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1642,22 +1657,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920112</v>
+        <v>22330051920342</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1665,16 +1680,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920342</v>
+        <v>22330051920126</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1688,22 +1703,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920150</v>
+        <v>22330051920132</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1711,22 +1726,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920384</v>
+        <v>22330051920258</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1734,16 +1749,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920158</v>
+        <v>22330051920150</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1757,16 +1772,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920176</v>
+        <v>22330051920384</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1775,6 +1790,52 @@
         <v>14</v>
       </c>
       <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920158</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -85,205 +85,139 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LEYVA</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VELASQUEZ</t>
-  </si>
-  <si>
     <t>DELGADO</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>KARLA ABIGAIL</t>
+    <t>ABIEL NEFTALI</t>
   </si>
   <si>
     <t>CAROLINA</t>
   </si>
   <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>DAMON</t>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
+    <t>LEONOR</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
   </si>
   <si>
     <t>GUSTAVO KALEL</t>
   </si>
   <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>BETZABE</t>
-  </si>
-  <si>
-    <t>TOBIAS</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
+    <t>ZURI GABRIELA</t>
   </si>
   <si>
     <t>NERY JOSELYN</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>MELANIE</t>
   </si>
   <si>
     <t>AXEL GAEL</t>
@@ -687,10 +621,10 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -699,7 +633,7 @@
         <v>76.47</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,22 +644,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -739,19 +673,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -765,19 +699,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -791,19 +725,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>60.47</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -814,22 +748,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>90.7</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -882,16 +816,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70.59</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -902,19 +839,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -928,16 +868,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
         <v>34</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -951,16 +894,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -974,16 +920,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>67.44</v>
+      </c>
+      <c r="H6">
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -994,19 +943,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>86.05</v>
+      </c>
+      <c r="H7">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1059,10 +1011,10 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -1071,7 +1023,7 @@
         <v>76.47</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1082,19 +1034,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
       <c r="F3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1111,10 +1063,10 @@
         <v>40</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>6</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>34</v>
@@ -1123,7 +1075,7 @@
         <v>85</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1137,16 +1089,16 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>86.36</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -1163,19 +1115,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>60.47</v>
+        <v>67.44</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1186,22 +1138,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>86.05</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1249,10 +1201,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1266,16 +1218,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920041</v>
+        <v>22330051920047</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1295,10 +1247,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1312,22 +1264,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920067</v>
+        <v>22330051920247</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1335,22 +1287,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920337</v>
+        <v>22330051920136</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1358,16 +1310,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920346</v>
+        <v>22330051920141</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1381,22 +1333,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920247</v>
+        <v>22330051920160</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1404,62 +1356,62 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920348</v>
+        <v>22330051920021</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920136</v>
+        <v>22330051920079</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920141</v>
+        <v>22330051920343</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1468,21 +1420,21 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920354</v>
+        <v>22330051920342</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1491,73 +1443,73 @@
         <v>13</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920155</v>
+        <v>22330051920126</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920386</v>
+        <v>22330051920346</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920021</v>
+        <v>22330051920138</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1565,22 +1517,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920334</v>
+        <v>22330051920258</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1588,254 +1540,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920079</v>
+        <v>22330051920176</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920112</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920124</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920342</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920126</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920132</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920258</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920150</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920384</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920158</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920176</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -82,22 +82,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>COCOTLE</t>
@@ -106,46 +109,31 @@
     <t>MEJIA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ARZATE</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
   </si>
   <si>
     <t>TEQUILIQUIHUA</t>
@@ -154,43 +142,31 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
     <t>ABIEL NEFTALI</t>
   </si>
   <si>
-    <t>CAROLINA</t>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
-    <t>BELEN</t>
+    <t>ACSA FERNANDA</t>
   </si>
   <si>
     <t>MARIAM</t>
@@ -199,28 +175,13 @@
     <t>JOSE FRANCISCO</t>
   </si>
   <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
     <t>LUCIANA</t>
   </si>
   <si>
     <t>LEONOR</t>
   </si>
   <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
     <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>NERY JOSELYN</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1195,22 +1156,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920047</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1218,22 +1179,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920047</v>
+        <v>22330051920079</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1241,22 +1202,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920065</v>
+        <v>22330051920126</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1264,16 +1225,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920247</v>
+        <v>22330051920244</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1287,16 +1248,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920136</v>
+        <v>22330051920346</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1310,16 +1271,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920141</v>
+        <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1333,22 +1294,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920160</v>
+        <v>22330051920144</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1356,45 +1317,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920021</v>
+        <v>22330051920160</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920079</v>
+        <v>22330051920021</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1408,10 +1369,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1431,10 +1392,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1448,16 +1409,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920126</v>
+        <v>22330051920138</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1466,98 +1427,6 @@
         <v>13</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920346</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920138</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920258</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920176</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -106,9 +115,6 @@
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>ARZATE</t>
   </si>
   <si>
@@ -118,12 +124,18 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -139,15 +151,21 @@
     <t>TEQUILIQUIHUA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
     <t>ABIEL NEFTALI</t>
   </si>
   <si>
@@ -170,9 +188,6 @@
   </si>
   <si>
     <t>MARIAM</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
   </si>
   <si>
     <t>LUCIANA</t>
@@ -1124,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1156,22 +1171,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920047</v>
+        <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1179,22 +1194,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920079</v>
+        <v>22330051920021</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1202,22 +1217,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920126</v>
+        <v>22330051920322</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1225,22 +1240,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920244</v>
+        <v>22330051920047</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1248,22 +1263,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920346</v>
+        <v>22330051920079</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1271,16 +1286,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920247</v>
+        <v>22330051920126</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1294,16 +1309,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920144</v>
+        <v>22330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1317,22 +1332,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920160</v>
+        <v>22330051920346</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1340,7 +1355,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920021</v>
+        <v>22330051920247</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1349,30 +1364,30 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920343</v>
+        <v>22330051920144</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1381,44 +1396,44 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920342</v>
+        <v>22330051920160</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920138</v>
+        <v>22330051920343</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1427,6 +1442,52 @@
         <v>13</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920342</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>PANZO</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -115,6 +112,12 @@
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>ARZATE</t>
   </si>
   <si>
@@ -133,9 +136,6 @@
     <t>MACARIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -151,6 +151,12 @@
     <t>TEQUILIQUIHUA</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -166,9 +172,6 @@
     <t>SHERLIN</t>
   </si>
   <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
     <t>MELANIE SOFIA</t>
   </si>
   <si>
@@ -188,6 +191,12 @@
   </si>
   <si>
     <t>MARIAM</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
   </si>
   <si>
     <t>LUCIANA</t>
@@ -792,7 +801,7 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -804,7 +813,7 @@
         <v>70.59</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -990,13 +999,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -1139,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1177,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1200,10 +1209,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1223,10 +1232,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1240,22 +1249,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920047</v>
+        <v>22330051920079</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1263,22 +1272,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920079</v>
+        <v>22330051920126</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1286,16 +1295,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1309,16 +1318,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920244</v>
+        <v>22330051920346</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1332,16 +1341,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1355,16 +1364,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920247</v>
+        <v>22330051920144</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1378,22 +1387,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920144</v>
+        <v>22330051920160</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1401,45 +1410,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920160</v>
+        <v>22330051920320</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920343</v>
+        <v>22330051920018</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1447,16 +1456,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920342</v>
+        <v>22330051920343</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1470,16 +1479,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920138</v>
+        <v>22330051920342</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1488,6 +1497,29 @@
         <v>13</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920138</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -88,36 +88,36 @@
     <t>MEJIA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>PANZO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>ARZATE</t>
   </si>
   <si>
@@ -133,30 +133,30 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
     <t>MACARIO</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -169,34 +169,34 @@
     <t>JOSE FRANCISCO</t>
   </si>
   <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
     <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
   <si>
     <t>LUCIANA</t>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920322</v>
+        <v>22330051920079</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
@@ -1241,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1249,13 +1249,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920079</v>
+        <v>22330051920126</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -1264,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920126</v>
+        <v>22330051920244</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920244</v>
+        <v>22330051920346</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1318,13 +1318,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -1341,13 +1341,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920247</v>
+        <v>22330051920144</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>55</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920144</v>
+        <v>22330051920160</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1379,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920160</v>
+        <v>22330051920320</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1402,15 +1402,15 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920320</v>
+        <v>22330051920018</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920018</v>
+        <v>22330051920322</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1462,7 +1462,7 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
         <v>60</v>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -85,36 +85,45 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>MEJIA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -127,33 +136,39 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
@@ -166,34 +181,43 @@
     <t>ANA KAREN</t>
   </si>
   <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>EIDAN JOSEPH</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
     <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
   <si>
     <t>SHERLIN</t>
@@ -1148,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1186,10 +1210,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1203,16 +1227,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920021</v>
+        <v>22330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1226,22 +1250,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920079</v>
+        <v>22330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1249,22 +1273,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920126</v>
+        <v>22330051920047</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1272,22 +1296,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920244</v>
+        <v>22330051920079</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1295,16 +1319,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920346</v>
+        <v>22330051920126</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1318,16 +1342,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920247</v>
+        <v>22330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1341,16 +1365,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920144</v>
+        <v>22330051920346</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1364,22 +1388,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920160</v>
+        <v>22330051920247</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1387,62 +1411,62 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920320</v>
+        <v>22330051920144</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920018</v>
+        <v>22330051920160</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920322</v>
+        <v>22330051920320</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1456,22 +1480,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920343</v>
+        <v>22330051920018</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1479,22 +1503,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920342</v>
+        <v>22330051920021</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1502,24 +1526,93 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920138</v>
+        <v>22330051920322</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920343</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G16">
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920342</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -82,151 +82,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>EIDAN JOSEPH</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
+    <t>LEONOR</t>
   </si>
   <si>
     <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
   </si>
   <si>
     <t>ZURI GABRIELA</t>
@@ -1023,16 +948,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1049,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1075,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -1153,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H7">
         <v>6.8</v>
@@ -1172,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1204,22 +1129,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1227,22 +1152,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920244</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1250,22 +1175,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920028</v>
+        <v>22330051920346</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1273,22 +1198,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920047</v>
+        <v>22330051920247</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1296,22 +1221,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920079</v>
+        <v>22330051920144</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1319,16 +1244,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920126</v>
+        <v>22330051920343</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1337,21 +1262,21 @@
         <v>13</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920244</v>
+        <v>22330051920342</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
         <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1360,21 +1285,21 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920346</v>
+        <v>22330051920126</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
         <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1383,21 +1308,21 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920247</v>
+        <v>22330051920138</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1406,213 +1331,6 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920160</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920320</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920018</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920021</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920322</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920343</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920342</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920138</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -82,79 +82,79 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>ARZATE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>LUNA</t>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>MEZA</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>KAREN</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>ALEXIS</t>
+    <t>LUCIANA</t>
+  </si>
+  <si>
+    <t>LEONOR</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
   </si>
   <si>
     <t>GUSTAVO KALEL</t>
   </si>
   <si>
-    <t>KAREN</t>
+    <t>ZURI GABRIELA</t>
   </si>
   <si>
     <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920105</v>
+        <v>22330051920244</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1144,7 +1144,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1152,13 +1152,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920244</v>
+        <v>22330051920247</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>38</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920346</v>
+        <v>22330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
@@ -1190,21 +1190,21 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920247</v>
+        <v>22330051920343</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
@@ -1216,18 +1216,18 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920144</v>
+        <v>22330051920342</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
         <v>41</v>
@@ -1239,18 +1239,18 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920343</v>
+        <v>22330051920126</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920342</v>
+        <v>22330051920346</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920126</v>
+        <v>22330051920138</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920138</v>
+        <v>22330051920144</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,81 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1026,13 +951,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -1052,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>67.44</v>
+        <v>90.7</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1097,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1127,213 +1052,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920244</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920247</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920105</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920343</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920342</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920126</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920346</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920138</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920144</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
